--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1281,6 +1281,9 @@
       <c r="C51" t="n">
         <v>2.181</v>
       </c>
+      <c r="D51" t="n">
+        <v>350864417.6</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">

--- a/docs/pension_data_combined_2026-09-10.xlsx
+++ b/docs/pension_data_combined_2026-09-10.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.144</v>
-      </c>
       <c r="D48" t="n">
         <v>4061522.58</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-09-10</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.1874</v>
       </c>
       <c r="D55" t="n">
         <v>59159832.74</v>
